--- a/Assets/Editor/Data_Table.xlsx
+++ b/Assets/Editor/Data_Table.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13080" windowHeight="13920" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Role" sheetId="1" r:id="rId1"/>
     <sheet name="Food" sheetId="2" r:id="rId2"/>
     <sheet name="Gift" sheetId="3" r:id="rId3"/>
-    <sheet name="Plant" sheetId="4" r:id="rId4"/>
+    <sheet name="Cloth" sheetId="5" r:id="rId4"/>
+    <sheet name="Plant" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -353,6 +354,54 @@
     <t>UI/Sprite/Gift/鸡排饭</t>
   </si>
   <si>
+    <t>帽子01</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子01</t>
+  </si>
+  <si>
+    <t>帽子02</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子02</t>
+  </si>
+  <si>
+    <t>帽子03</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子03</t>
+  </si>
+  <si>
+    <t>帽子04</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子04</t>
+  </si>
+  <si>
+    <t>帽子05</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子05</t>
+  </si>
+  <si>
+    <t>帽子06</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子06</t>
+  </si>
+  <si>
+    <t>帽子07</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子07</t>
+  </si>
+  <si>
+    <t>帽子08</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Cloth/帽子08</t>
+  </si>
+  <si>
     <t>Reward</t>
   </si>
   <si>
@@ -383,7 +432,13 @@
     <t>Harvest_Num</t>
   </si>
   <si>
-    <t>Germinate_SpriteRes</t>
+    <t>Germinate_SpriteResPath</t>
+  </si>
+  <si>
+    <t>Grown_SpriteResPath</t>
+  </si>
+  <si>
+    <t>Mature_SpriteResPath</t>
   </si>
   <si>
     <t>植物ID:
@@ -399,16 +454,16 @@
     <t>卖出收入</t>
   </si>
   <si>
-    <t>发芽时间</t>
-  </si>
-  <si>
-    <t>成长时间</t>
-  </si>
-  <si>
-    <t>成熟时间</t>
-  </si>
-  <si>
-    <t>种植时间</t>
+    <t>发芽时间（秒）</t>
+  </si>
+  <si>
+    <t>成长时间（秒）</t>
+  </si>
+  <si>
+    <t>成熟时间（秒）</t>
+  </si>
+  <si>
+    <t>种植时间（秒）</t>
   </si>
   <si>
     <t>浇水时间</t>
@@ -426,16 +481,61 @@
     <t>收获数量</t>
   </si>
   <si>
-    <t>植物发芽图片
-对应资源</t>
-  </si>
-  <si>
-    <t>植物生长图片
-对应资源</t>
-  </si>
-  <si>
-    <t>植物成熟图片
-对应资源</t>
+    <t>植物发芽期
+对应图片资源</t>
+  </si>
+  <si>
+    <t>植物生长期
+对应图片资源</t>
+  </si>
+  <si>
+    <t>植物成熟期
+对应图片资源</t>
+  </si>
+  <si>
+    <t>P基因小麦</t>
+  </si>
+  <si>
+    <t>P过基因的小麦，但基因不能p所以是真的</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/P基因小麦萌芽期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/P基因小麦生长期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/P基因小麦成熟期</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>玉玉的米</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/玉米萌芽期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/玉米生长期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/玉米成熟期</t>
+  </si>
+  <si>
+    <t>西蓝柿</t>
+  </si>
+  <si>
+    <t>潘多拉土产柿子</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/西蓝柿萌芽期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/西蓝柿生长期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/P基因小麦/西蓝柿成熟期</t>
   </si>
 </sst>
 </file>
@@ -2211,23 +2311,233 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="28.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" ht="42.75" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>1002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>1004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>1005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>1006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>1007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>1008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="6.08333333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="35.375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="6" max="6" width="13.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="11.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="10.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
     <col min="11" max="11" width="11.9166666666667" customWidth="1"/>
     <col min="12" max="12" width="14.4166666666667" customWidth="1"/>
     <col min="13" max="13" width="13.5833333333333" customWidth="1"/>
     <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="15" max="15" width="17.4166666666667" customWidth="1"/>
-    <col min="16" max="16" width="17.0833333333333" customWidth="1"/>
-    <col min="17" max="17" width="16.5" customWidth="1"/>
+    <col min="15" max="15" width="37.25" customWidth="1"/>
+    <col min="16" max="16" width="40.25" customWidth="1"/>
+    <col min="17" max="17" width="39.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -2241,99 +2551,99 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="N1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="O1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="P1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="Q1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="K2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="L2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="M2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="N2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2389,70 +2699,194 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:17">
       <c r="A4" s="3">
         <v>1001</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="3">
         <v>1002</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>151</v>
+      </c>
+      <c r="P5" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="3">
         <v>1003</v>
       </c>
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P6" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3">
-        <v>1004</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3">
-        <v>1005</v>
-      </c>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3">
-        <v>1006</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="3">
-        <v>1007</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3">
-        <v>1008</v>
-      </c>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3">
-        <v>1009</v>
-      </c>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3">
-        <v>1010</v>
-      </c>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3">
-        <v>1011</v>
-      </c>
+      <c r="A14" s="3"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3">
-        <v>1012</v>
-      </c>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="3">
-        <v>1013</v>
-      </c>
+      <c r="A16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Editor/Data_Table.xlsx
+++ b/Assets/Editor/Data_Table.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Role" sheetId="1" r:id="rId1"/>
-    <sheet name="Food" sheetId="2" r:id="rId2"/>
+    <sheet name="RoleData" sheetId="1" r:id="rId1"/>
+    <sheet name="RoleInformation" sheetId="6" r:id="rId2"/>
     <sheet name="Gift" sheetId="3" r:id="rId3"/>
-    <sheet name="Cloth" sheetId="5" r:id="rId4"/>
-    <sheet name="Plant" sheetId="4" r:id="rId5"/>
+    <sheet name="Food" sheetId="2" r:id="rId4"/>
+    <sheet name="Cloth" sheetId="5" r:id="rId5"/>
+    <sheet name="Plant" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,30 +32,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="170">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>CharacterName</t>
-  </si>
-  <si>
-    <t>Hobby</t>
-  </si>
-  <si>
-    <t>Personality</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Birthday</t>
-  </si>
-  <si>
     <t>Favorability</t>
   </si>
   <si>
-    <t>FavorvateThing</t>
+    <t>FavorvateThing_ID</t>
+  </si>
+  <si>
+    <t>CherishThing_ID</t>
   </si>
   <si>
     <t>MoveSpeed</t>
@@ -81,29 +70,16 @@
     <t>Skel</t>
   </si>
   <si>
-    <t>角色ID</t>
-  </si>
-  <si>
-    <t>角色名称</t>
-  </si>
-  <si>
-    <t>爱好</t>
-  </si>
-  <si>
-    <t>个性</t>
-  </si>
-  <si>
-    <t>角色描述</t>
-  </si>
-  <si>
-    <t>生日</t>
-  </si>
-  <si>
-    <t>好感度</t>
-  </si>
-  <si>
-    <t>喜欢的东西/小动
-物收到喜欢的礼物有额外好感度加成</t>
+    <t>角色ID（1001~1999）</t>
+  </si>
+  <si>
+    <t>初始好感度</t>
+  </si>
+  <si>
+    <t>喜欢的物品</t>
+  </si>
+  <si>
+    <t>珍爱的物品</t>
   </si>
   <si>
     <t>行走速度</t>
@@ -137,10 +113,46 @@
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
+    <t>UI/Sprite/Role/瑞贝特</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Role/羊童木</t>
+  </si>
+  <si>
+    <t>CharacterName</t>
+  </si>
+  <si>
+    <t>Hobby</t>
+  </si>
+  <si>
+    <t>Personality</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Birthday</t>
+  </si>
+  <si>
+    <t>角色名称</t>
+  </si>
+  <si>
+    <t>爱好</t>
+  </si>
+  <si>
+    <t>个性</t>
+  </si>
+  <si>
+    <t>角色描述</t>
+  </si>
+  <si>
+    <t>生日</t>
   </si>
   <si>
     <t>瑞贝特</t>
@@ -158,9 +170,6 @@
     <t>2000.1.1</t>
   </si>
   <si>
-    <t>UI/Sprite/Role/瑞贝特</t>
-  </si>
-  <si>
     <t>羊童木</t>
   </si>
   <si>
@@ -170,7 +179,15 @@
     <t>沉稳</t>
   </si>
   <si>
-    <t>UI/Sprite/Role/羊童木</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Id</t>
+    </r>
   </si>
   <si>
     <t>Name</t>
@@ -179,14 +196,17 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>ResPath</t>
-  </si>
-  <si>
-    <t>食物ID:
-1001~1999</t>
+    <t>Default_Affinity</t>
+  </si>
+  <si>
+    <t>Like_Affinity</t>
+  </si>
+  <si>
+    <t>Favorate_Affinity</t>
+  </si>
+  <si>
+    <t>礼物ID:
+2001~2999</t>
   </si>
   <si>
     <t>Item名称</t>
@@ -195,14 +215,19 @@
     <t>食物描述</t>
   </si>
   <si>
-    <t>买入花费
-从食堂买入食品后每次小动物进食都扣除等量花费</t>
-  </si>
-  <si>
-    <t>小动物进食后获得的数值加成（还不知道加在哪里）</t>
-  </si>
-  <si>
-    <t>食物对应美术资源</t>
+    <t>买入花费</t>
+  </si>
+  <si>
+    <t>默认好感度</t>
+  </si>
+  <si>
+    <t>喜爱好感度</t>
+  </si>
+  <si>
+    <t>最高好感度</t>
+  </si>
+  <si>
+    <t>礼物对应美术资源</t>
   </si>
   <si>
     <r>
@@ -216,6 +241,103 @@
     </r>
   </si>
   <si>
+    <t>每年达</t>
+  </si>
+  <si>
+    <t>每年都发达</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/健康套餐</t>
+  </si>
+  <si>
+    <t>卡布奇诺</t>
+  </si>
+  <si>
+    <t>卡不得奇诺</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/卡布奇诺</t>
+  </si>
+  <si>
+    <t>咖喱饭</t>
+  </si>
+  <si>
+    <t>咖喱的饭</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/咖喱饭</t>
+  </si>
+  <si>
+    <t>拿铁</t>
+  </si>
+  <si>
+    <t>拿拿的铁</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/拿铁</t>
+  </si>
+  <si>
+    <t>有猫可乐</t>
+  </si>
+  <si>
+    <t>有猫集团诚意出品</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/有猫可乐</t>
+  </si>
+  <si>
+    <t>每年都达</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/每年达</t>
+  </si>
+  <si>
+    <t>老山美式</t>
+  </si>
+  <si>
+    <t>崂山的美式</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/老山美式</t>
+  </si>
+  <si>
+    <t>草莓奶昔</t>
+  </si>
+  <si>
+    <t>草莓的奶昔</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/草莓奶昔</t>
+  </si>
+  <si>
+    <t>鸡排饭</t>
+  </si>
+  <si>
+    <t>鸡鸡的排</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Gift/鸡排饭</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>ResPath</t>
+  </si>
+  <si>
+    <t>食物ID:
+3001~3999</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>小动物进食后获得的数值加成（还不知道加在哪里）</t>
+  </si>
+  <si>
+    <t>食物对应美术资源</t>
+  </si>
+  <si>
     <t>健康套餐</t>
   </si>
   <si>
@@ -225,133 +347,35 @@
     <t>UI/Sprite/Food/健康套餐</t>
   </si>
   <si>
-    <t>卡布奇诺</t>
-  </si>
-  <si>
-    <t>卡不得奇诺</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/卡布奇诺</t>
   </si>
   <si>
-    <t>咖喱饭</t>
-  </si>
-  <si>
-    <t>咖喱的饭</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/咖喱饭</t>
   </si>
   <si>
-    <t>拿铁</t>
-  </si>
-  <si>
-    <t>拿拿的铁</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/拿铁</t>
   </si>
   <si>
-    <t>有猫可乐</t>
-  </si>
-  <si>
     <t>有猫的可乐</t>
   </si>
   <si>
     <t>UI/Sprite/Food/有猫可乐</t>
   </si>
   <si>
-    <t>每年达</t>
-  </si>
-  <si>
-    <t>每年都达</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/每年达</t>
   </si>
   <si>
-    <t>老山美式</t>
-  </si>
-  <si>
-    <t>崂山的美式</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/老山美式</t>
   </si>
   <si>
-    <t>草莓奶昔</t>
-  </si>
-  <si>
-    <t>草莓的奶昔</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/草莓奶昔</t>
   </si>
   <si>
-    <t>鸡排饭</t>
-  </si>
-  <si>
-    <t>鸡鸡的排</t>
-  </si>
-  <si>
     <t>UI/Sprite/Food/鸡排饭</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Id</t>
-    </r>
-  </si>
-  <si>
-    <t>Affection Bonus</t>
-  </si>
-  <si>
-    <t>礼物ID:
-1001~1999</t>
-  </si>
-  <si>
-    <t>买入花费</t>
-  </si>
-  <si>
-    <t>好感度加成</t>
-  </si>
-  <si>
-    <t>礼物对应美术资源</t>
-  </si>
-  <si>
-    <t>每年都发达</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/健康套餐</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/卡布奇诺</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/咖喱饭</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/拿铁</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/有猫可乐</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/每年达</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/老山美式</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/草莓奶昔</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Gift/鸡排饭</t>
+    <t>衣物ID:
+4001~4999</t>
   </si>
   <si>
     <t>帽子01</t>
@@ -405,24 +429,30 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>Plant_Time</t>
+  </si>
+  <si>
     <t>Germinate_Time</t>
   </si>
   <si>
-    <t>Grown_Time</t>
+    <t>fertilize_Time</t>
+  </si>
+  <si>
+    <t>Grown_Time1</t>
+  </si>
+  <si>
+    <t>Water_Time1</t>
+  </si>
+  <si>
+    <t>Grown_Time2</t>
+  </si>
+  <si>
+    <t>Water_Time2</t>
   </si>
   <si>
     <t>Mature_Time</t>
   </si>
   <si>
-    <t>Plant_Time</t>
-  </si>
-  <si>
-    <t>Water_Time</t>
-  </si>
-  <si>
-    <t>fertilize_Time</t>
-  </si>
-  <si>
     <t>BugControl_Time</t>
   </si>
   <si>
@@ -442,7 +472,7 @@
   </si>
   <si>
     <t>植物ID:
-1001~1999</t>
+5001~5999</t>
   </si>
   <si>
     <t>名称</t>
@@ -454,22 +484,25 @@
     <t>卖出收入</t>
   </si>
   <si>
-    <t>发芽时间（秒）</t>
-  </si>
-  <si>
-    <t>成长时间（秒）</t>
-  </si>
-  <si>
-    <t>成熟时间（秒）</t>
-  </si>
-  <si>
-    <t>种植时间（秒）</t>
-  </si>
-  <si>
-    <t>浇水时间</t>
+    <t>种植时间（人工）</t>
+  </si>
+  <si>
+    <t>发芽时间（自动）</t>
   </si>
   <si>
     <t>施肥时间</t>
+  </si>
+  <si>
+    <t>成长时间（自动）</t>
+  </si>
+  <si>
+    <t>浇水单元1</t>
+  </si>
+  <si>
+    <t>浇水单元2</t>
+  </si>
+  <si>
+    <t>成熟时间（自动）</t>
   </si>
   <si>
     <t>除虫时间</t>
@@ -514,13 +547,13 @@
     <t>玉玉的米</t>
   </si>
   <si>
-    <t>UI/Sprite/Plant/P基因小麦/玉米萌芽期</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Plant/P基因小麦/玉米生长期</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Plant/P基因小麦/玉米成熟期</t>
+    <t>UI/Sprite/Plant/玉米/玉米萌芽期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/玉米/玉米生长期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/玉米/玉米成熟期</t>
   </si>
   <si>
     <t>西蓝柿</t>
@@ -529,13 +562,13 @@
     <t>潘多拉土产柿子</t>
   </si>
   <si>
-    <t>UI/Sprite/Plant/P基因小麦/西蓝柿萌芽期</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Plant/P基因小麦/西蓝柿生长期</t>
-  </si>
-  <si>
-    <t>UI/Sprite/Plant/P基因小麦/西蓝柿成熟期</t>
+    <t>UI/Sprite/Plant/西蓝柿/西蓝柿萌芽期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/西蓝柿/西蓝柿生长期</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Plant/西蓝柿/西蓝柿成熟期</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1173,6 +1206,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1190,6 +1226,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1513,33 +1555,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="14.0833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="7" max="7" width="12.4166666666667" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="9" max="9" width="12.8333333333333" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.8333333333333" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="13.0833333333333" customWidth="1"/>
-    <col min="14" max="14" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="12.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="23.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="10" customWidth="1"/>
+    <col min="5" max="5" width="12.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.4166666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="24.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1557,209 +1598,154 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" ht="130" customHeight="1" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="130" customHeight="1" spans="1:16">
-      <c r="A2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="K3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>1001</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>2001</v>
+      </c>
+      <c r="D4" s="11">
+        <v>2003</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4"/>
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
       <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>40</v>
-      </c>
-      <c r="L4">
-        <v>10</v>
-      </c>
-      <c r="M4">
         <v>100</v>
       </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>1002</v>
       </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>2002</v>
+      </c>
+      <c r="D5" s="11">
+        <v>2004</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>40</v>
-      </c>
-      <c r="L5">
-        <v>10</v>
-      </c>
-      <c r="M5">
         <v>100</v>
       </c>
-      <c r="N5" t="s">
-        <v>44</v>
+      <c r="J5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1771,267 +1757,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="11.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="20.5833333333333" customWidth="1"/>
+    <col min="1" max="1" width="20.625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="26.125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9" style="10"/>
+    <col min="5" max="5" width="15.75" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" ht="69" customHeight="1" spans="1:6">
+      <c r="A2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="10">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="10">
+        <v>1002</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" ht="104" customHeight="1" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:6">
-      <c r="A5" s="3">
-        <v>1002</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="29" customHeight="1" spans="1:6">
-      <c r="A6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1" spans="1:6">
-      <c r="A7" s="3">
-        <v>1004</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:6">
-      <c r="A8" s="3">
-        <v>1005</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:6">
-      <c r="A9" s="3">
-        <v>1006</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" spans="1:6">
-      <c r="A10" s="3">
-        <v>1007</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10">
-        <v>70</v>
-      </c>
-      <c r="E10">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:6">
-      <c r="A11" s="3">
-        <v>1008</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11">
-        <v>80</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" ht="37" customHeight="1" spans="1:6">
-      <c r="A12" s="3">
-        <v>1009</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12">
-        <v>90</v>
-      </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="3"/>
+      <c r="E5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2042,163 +1877,208 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="3" max="3" width="10.5833333333333" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
     <col min="5" max="5" width="15.9166666666667" customWidth="1"/>
-    <col min="6" max="6" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
+    <col min="8" max="8" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" ht="42.75" spans="1:6">
+        <v>32</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="73" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>87</v>
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>58</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3">
-        <v>1001</v>
+        <v>24</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4">
+        <v>2001</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3">
-        <v>1002</v>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4">
+        <v>2002</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3">
-        <v>1003</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4">
+        <v>2003</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3">
-        <v>1004</v>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4">
+        <v>2004</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>40</v>
       </c>
       <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3">
-        <v>1005</v>
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4">
+        <v>2005</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2206,101 +2086,131 @@
       <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3">
-        <v>1006</v>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="4">
+        <v>2006</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
       <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3">
-        <v>1007</v>
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4">
+        <v>2007</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>70</v>
       </c>
       <c r="E10">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3">
-        <v>1008</v>
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4">
+        <v>2008</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D11">
         <v>80</v>
       </c>
       <c r="E11">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3">
-        <v>1009</v>
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4">
+        <v>2009</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D12">
         <v>90</v>
       </c>
       <c r="E12">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>98</v>
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3"/>
+      <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="3"/>
+      <c r="A16" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2311,206 +2221,265 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="5" max="5" width="27.5" customWidth="1"/>
-    <col min="6" max="6" width="28.875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" ht="42.75" spans="1:6">
+        <v>88</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" ht="104" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>86</v>
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F2" s="8"/>
+        <v>92</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3">
-        <v>1001</v>
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6">
+      <c r="A4" s="4">
+        <v>3001</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3">
-        <v>1002</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:6">
+      <c r="A5" s="4">
+        <v>3002</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>1003</v>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1" spans="1:6">
+      <c r="A6" s="4">
+        <v>3003</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
-        <v>1004</v>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" spans="1:6">
+      <c r="A7" s="4">
+        <v>3004</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
-        <v>1005</v>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6">
+      <c r="A8" s="4">
+        <v>3005</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>50</v>
       </c>
-      <c r="E8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3">
-        <v>1006</v>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:6">
+      <c r="A9" s="4">
+        <v>3006</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3">
-        <v>1007</v>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:6">
+      <c r="A10" s="4">
+        <v>3007</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3">
-        <v>1008</v>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:6">
+      <c r="A11" s="4">
+        <v>3008</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D11">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="3"/>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" ht="37" customHeight="1" spans="1:6">
+      <c r="A12" s="4">
+        <v>3009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12">
+        <v>90</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2521,199 +2490,430 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="28.8333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" ht="42.75" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4">
+        <v>4001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4">
+        <v>4002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4">
+        <v>4003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4">
+        <v>4004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4">
+        <v>4005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4">
+        <v>4006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4">
+        <v>4007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4">
+        <v>4008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="3" width="35.375" customWidth="1"/>
+    <col min="2" max="2" width="12.5833333333333" customWidth="1"/>
+    <col min="3" max="3" width="35.3333333333333" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="9" width="14.375" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="11.9166666666667" customWidth="1"/>
-    <col min="12" max="12" width="14.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="13.5833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="15" max="15" width="37.25" customWidth="1"/>
-    <col min="16" max="16" width="40.25" customWidth="1"/>
-    <col min="17" max="17" width="39.375" customWidth="1"/>
+    <col min="6" max="6" width="14.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="11.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="10" width="12.8333333333333" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="12.8333333333333" customWidth="1"/>
+    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="13.5833333333333" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
+    <col min="17" max="17" width="37.25" customWidth="1"/>
+    <col min="18" max="18" width="40.25" customWidth="1"/>
+    <col min="19" max="19" width="39.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="K1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L1" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="M1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="N1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="O1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="P1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="Q1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" ht="73" customHeight="1" spans="1:17">
+        <v>135</v>
+      </c>
+      <c r="R1" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" ht="73" customHeight="1" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" t="s">
-        <v>133</v>
+        <v>56</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L2" t="s">
-        <v>138</v>
-      </c>
-      <c r="M2" t="s">
-        <v>139</v>
+        <v>144</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="N2" t="s">
-        <v>140</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>149</v>
+      </c>
+      <c r="O2" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="3">
-        <v>1001</v>
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="4">
+        <v>5001</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
         <v>5</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -2740,33 +2940,39 @@
         <v>10</v>
       </c>
       <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="P4">
         <v>3</v>
       </c>
-      <c r="O4" t="s">
-        <v>146</v>
-      </c>
-      <c r="P4" t="s">
-        <v>147</v>
-      </c>
       <c r="Q4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="3">
-        <v>1002</v>
+        <v>157</v>
+      </c>
+      <c r="R4" t="s">
+        <v>158</v>
+      </c>
+      <c r="S4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="4">
+        <v>5002</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -2787,39 +2993,45 @@
         <v>20</v>
       </c>
       <c r="L5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>20</v>
       </c>
       <c r="N5">
+        <v>20</v>
+      </c>
+      <c r="O5">
+        <v>20</v>
+      </c>
+      <c r="P5">
         <v>3</v>
       </c>
-      <c r="O5" t="s">
-        <v>151</v>
-      </c>
-      <c r="P5" t="s">
-        <v>152</v>
-      </c>
       <c r="Q5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="3">
-        <v>1003</v>
+        <v>162</v>
+      </c>
+      <c r="R5" t="s">
+        <v>163</v>
+      </c>
+      <c r="S5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="4">
+        <v>5003</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>30</v>
@@ -2840,53 +3052,62 @@
         <v>30</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>30</v>
       </c>
       <c r="N6">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>30</v>
+      </c>
+      <c r="P6">
         <v>3</v>
       </c>
-      <c r="O6" t="s">
-        <v>156</v>
-      </c>
-      <c r="P6" t="s">
-        <v>157</v>
-      </c>
       <c r="Q6" t="s">
-        <v>158</v>
+        <v>167</v>
+      </c>
+      <c r="R6" t="s">
+        <v>168</v>
+      </c>
+      <c r="S6" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="3"/>
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4"/>
+      <c r="G11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3"/>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3"/>
+      <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="3"/>
+      <c r="A16" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Editor/Data_Table.xlsx
+++ b/Assets/Editor/Data_Table.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="5"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="RoleData" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="173">
   <si>
     <t>ID</t>
   </si>
@@ -374,8 +374,17 @@
     <t>UI/Sprite/Food/鸡排饭</t>
   </si>
   <si>
+    <t>TargetAnimal</t>
+  </si>
+  <si>
     <t>衣物ID:
 4001~4999</t>
+  </si>
+  <si>
+    <t>衣物描述</t>
+  </si>
+  <si>
+    <t>衣物对应的小动物ID</t>
   </si>
   <si>
     <t>帽子01</t>
@@ -2494,8 +2503,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.5" customWidth="1"/>
-    <col min="6" max="6" width="28.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="28.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2512,27 +2521,31 @@
         <v>49</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="7"/>
     </row>
     <row r="2" ht="42.75" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -2548,144 +2561,170 @@
         <v>24</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>4001</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>1001</v>
+      </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <v>4002</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>1001</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <v>4003</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6">
+        <v>1001</v>
+      </c>
+      <c r="F6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="4">
         <v>4004</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>1001</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="4">
         <v>4005</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>50</v>
       </c>
-      <c r="E8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>1002</v>
+      </c>
+      <c r="F8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="4">
         <v>4006</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9">
+        <v>1002</v>
+      </c>
+      <c r="F9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="4">
         <v>4007</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D10">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>1002</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="4">
         <v>4008</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D11">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
-        <v>122</v>
+      <c r="E11">
+        <v>1002</v>
+      </c>
+      <c r="F11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -2733,111 +2772,111 @@
         <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E1" t="s">
         <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="S1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2904,10 +2943,10 @@
         <v>5001</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2949,13 +2988,13 @@
         <v>3</v>
       </c>
       <c r="Q4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="R4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="S4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2963,10 +3002,10 @@
         <v>5002</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -3008,13 +3047,13 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="R5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="S5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3022,10 +3061,10 @@
         <v>5003</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -3067,13 +3106,13 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:1">

--- a/Assets/Editor/Data_Table.xlsx
+++ b/Assets/Editor/Data_Table.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="RoleData" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="178">
   <si>
     <t>ID</t>
   </si>
@@ -125,6 +125,9 @@
     <t>UI/Sprite/Role/羊童木</t>
   </si>
   <si>
+    <t>UI/Sprite/Role/Player</t>
+  </si>
+  <si>
     <t>CharacterName</t>
   </si>
   <si>
@@ -177,6 +180,18 @@
   </si>
   <si>
     <t>沉稳</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>刷手机</t>
+  </si>
+  <si>
+    <t>内敛</t>
+  </si>
+  <si>
+    <t>2001.1.1</t>
   </si>
   <si>
     <r>
@@ -1564,8 +1579,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
     <col min="2" max="2" width="12.4166666666667" customWidth="1"/>
@@ -1757,6 +1772,38 @@
         <v>28</v>
       </c>
     </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>1003</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10">
+        <v>2003</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2005</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1766,8 +1813,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="13.625" style="10" customWidth="1"/>
@@ -1782,19 +1829,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="69" customHeight="1" spans="1:6">
@@ -1802,19 +1849,19 @@
         <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1842,19 +1889,19 @@
         <v>1001</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1862,19 +1909,39 @@
         <v>1002</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="10">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>43</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1954,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="3" max="3" width="16.25" customWidth="1"/>
@@ -1899,25 +1966,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>9</v>
@@ -1925,33 +1992,33 @@
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1980,10 +2047,10 @@
         <v>2001</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1998,7 +2065,7 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2006,10 +2073,10 @@
         <v>2002</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2024,7 +2091,7 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2032,10 +2099,10 @@
         <v>2003</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -2050,7 +2117,7 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2058,10 +2125,10 @@
         <v>2004</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -2076,7 +2143,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2084,10 +2151,10 @@
         <v>2005</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2102,7 +2169,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2110,10 +2177,10 @@
         <v>2006</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -2128,7 +2195,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2136,10 +2203,10 @@
         <v>2007</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2154,7 +2221,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2162,10 +2229,10 @@
         <v>2008</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2180,7 +2247,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2188,10 +2255,10 @@
         <v>2009</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -2206,7 +2273,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2231,7 +2298,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="6" max="6" width="20.5" customWidth="1"/>
@@ -2243,44 +2310,44 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" ht="104" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2303,10 +2370,10 @@
         <v>3001</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2315,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:6">
@@ -2323,10 +2390,10 @@
         <v>3002</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2335,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="29" customHeight="1" spans="1:6">
@@ -2343,10 +2410,10 @@
         <v>3003</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -2355,7 +2422,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:6">
@@ -2363,10 +2430,10 @@
         <v>3004</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -2375,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6">
@@ -2383,10 +2450,10 @@
         <v>3005</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2395,7 +2462,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:6">
@@ -2403,10 +2470,10 @@
         <v>3006</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -2415,7 +2482,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:6">
@@ -2423,10 +2490,10 @@
         <v>3007</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2435,7 +2502,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1" spans="1:6">
@@ -2443,10 +2510,10 @@
         <v>3008</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2455,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="37" customHeight="1" spans="1:6">
@@ -2463,10 +2530,10 @@
         <v>3009</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -2475,7 +2542,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2500,7 +2567,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
     <col min="5" max="5" width="28.8333333333333" customWidth="1"/>
@@ -2509,47 +2576,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="42.75" spans="1:6">
+    <row r="2" ht="42" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2572,10 +2639,10 @@
         <v>4001</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2584,7 +2651,7 @@
         <v>1001</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2592,10 +2659,10 @@
         <v>4002</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2604,7 +2671,7 @@
         <v>1001</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2612,10 +2679,10 @@
         <v>4003</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -2624,7 +2691,7 @@
         <v>1001</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2632,10 +2699,10 @@
         <v>4004</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -2644,7 +2711,7 @@
         <v>1001</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2652,10 +2719,10 @@
         <v>4005</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2664,7 +2731,7 @@
         <v>1002</v>
       </c>
       <c r="F8" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2672,10 +2739,10 @@
         <v>4006</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -2684,7 +2751,7 @@
         <v>1002</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2692,10 +2759,10 @@
         <v>4007</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2704,7 +2771,7 @@
         <v>1002</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2712,10 +2779,10 @@
         <v>4008</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2724,7 +2791,7 @@
         <v>1002</v>
       </c>
       <c r="F11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -2740,7 +2807,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.5833333333333" customWidth="1"/>
     <col min="3" max="3" width="35.3333333333333" customWidth="1"/>
@@ -2763,125 +2830,125 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="N1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="O1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="P1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="R1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="S1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="P2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2943,10 +3010,10 @@
         <v>5001</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2988,13 +3055,13 @@
         <v>3</v>
       </c>
       <c r="Q4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="R4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="S4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3002,10 +3069,10 @@
         <v>5002</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -3047,13 +3114,13 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="R5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="S5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3061,10 +3128,10 @@
         <v>5003</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -3106,13 +3173,13 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="R6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="S6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">

--- a/Assets/Editor/Data_Table.xlsx
+++ b/Assets/Editor/Data_Table.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12280" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RoleData" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Food" sheetId="2" r:id="rId4"/>
     <sheet name="Cloth" sheetId="5" r:id="rId5"/>
     <sheet name="Plant" sheetId="4" r:id="rId6"/>
+    <sheet name="Map" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="197">
   <si>
     <t>ID</t>
   </si>
@@ -128,6 +129,12 @@
     <t>UI/Sprite/Role/Player</t>
   </si>
   <si>
+    <t>UI/Sprite/Role/NekoGG</t>
+  </si>
+  <si>
+    <t>UI/Sprite/Role/NekoMM</t>
+  </si>
+  <si>
     <t>CharacterName</t>
   </si>
   <si>
@@ -192,6 +199,27 @@
   </si>
   <si>
     <t>2001.1.1</t>
+  </si>
+  <si>
+    <t>NekoGG</t>
+  </si>
+  <si>
+    <t>刷尾巴毛</t>
+  </si>
+  <si>
+    <t>阴沉</t>
+  </si>
+  <si>
+    <t>2002.1.1</t>
+  </si>
+  <si>
+    <t>NekoMM</t>
+  </si>
+  <si>
+    <t>刷已把毛</t>
+  </si>
+  <si>
+    <t>快乐</t>
   </si>
   <si>
     <r>
@@ -593,6 +621,36 @@
   </si>
   <si>
     <t>UI/Sprite/Plant/西蓝柿/西蓝柿成熟期</t>
+  </si>
+  <si>
+    <t>地图ID（6001~6999）</t>
+  </si>
+  <si>
+    <t>地图名称</t>
+  </si>
+  <si>
+    <t>地图描述</t>
+  </si>
+  <si>
+    <t>购入价格</t>
+  </si>
+  <si>
+    <t>地图资源位置</t>
+  </si>
+  <si>
+    <t>地图1</t>
+  </si>
+  <si>
+    <t>地图1的描述</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>地图2</t>
+  </si>
+  <si>
+    <t>地图2的描述</t>
   </si>
 </sst>
 </file>
@@ -1224,40 +1282,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1579,19 +1637,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
     <col min="2" max="2" width="12.4166666666667" customWidth="1"/>
-    <col min="3" max="3" width="23.375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="10" customWidth="1"/>
+    <col min="3" max="3" width="23.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.8333333333333" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="11.8333333333333" customWidth="1"/>
     <col min="8" max="8" width="13.4166666666667" customWidth="1"/>
     <col min="9" max="9" width="13.0833333333333" customWidth="1"/>
     <col min="10" max="10" width="24.5833333333333" customWidth="1"/>
+    <col min="11" max="11" width="20.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1601,10 +1660,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1622,13 +1681,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1636,13 +1695,13 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E2" t="s">
@@ -1651,22 +1710,22 @@
       <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1677,10 +1736,10 @@
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
@@ -1698,27 +1757,27 @@
       <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <v>2001</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="12">
         <v>2003</v>
       </c>
       <c r="E4">
@@ -1739,18 +1798,21 @@
       <c r="J4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>1002</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <v>2002</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="12">
         <v>2004</v>
       </c>
       <c r="E5">
@@ -1771,18 +1833,21 @@
       <c r="J5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>1003</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="1">
         <v>2003</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="1">
         <v>2005</v>
       </c>
       <c r="E6">
@@ -1802,6 +1867,79 @@
       </c>
       <c r="J6" t="s">
         <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>1004</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>1005</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1813,135 +1951,175 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="20.625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="26.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9" style="10"/>
-    <col min="5" max="5" width="15.75" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9" style="10"/>
+    <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" ht="69" customHeight="1" spans="1:6">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="10">
+      <c r="A4" s="1">
         <v>1001</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="E4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10">
+      <c r="A5" s="1">
         <v>1002</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10">
+      <c r="A6" s="1">
         <v>1003</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="C6" s="1" t="s">
         <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1965,60 +2143,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
+      <c r="A1" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>55</v>
+        <v>35</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>58</v>
+      <c r="A2" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>66</v>
+      <c r="A3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2026,31 +2204,31 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4">
+      <c r="A4" s="10">
         <v>2001</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2065,18 +2243,18 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>2002</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2091,18 +2269,18 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4">
+      <c r="A6" s="10">
         <v>2003</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -2117,18 +2295,18 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="4">
+      <c r="A7" s="10">
         <v>2004</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -2143,18 +2321,18 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="4">
+      <c r="A8" s="10">
         <v>2005</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2169,18 +2347,18 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4">
+      <c r="A9" s="10">
         <v>2006</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -2195,18 +2373,18 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4">
+      <c r="A10" s="10">
         <v>2007</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2221,18 +2399,18 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="4">
+      <c r="A11" s="10">
         <v>2008</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2247,18 +2425,18 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4">
+      <c r="A12" s="10">
         <v>2009</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -2273,20 +2451,20 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="10"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="10"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="10"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2306,48 +2484,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>94</v>
+        <v>35</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="104" customHeight="1" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>95</v>
+      <c r="A2" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>98</v>
+        <v>69</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>66</v>
+      <c r="A3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2355,25 +2533,25 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="10">
         <v>3001</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2381,19 +2559,19 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>101</v>
+      <c r="F4" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>3002</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2401,19 +2579,19 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>102</v>
+      <c r="F5" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="6" ht="29" customHeight="1" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="10">
         <v>3003</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -2422,18 +2600,18 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="10">
         <v>3004</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -2441,19 +2619,19 @@
       <c r="E7">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>104</v>
+      <c r="F7" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="10">
         <v>3005</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2461,19 +2639,19 @@
       <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>106</v>
+      <c r="F8" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="10">
         <v>3006</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -2481,19 +2659,19 @@
       <c r="E9">
         <v>6</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>107</v>
+      <c r="F9" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:6">
-      <c r="A10" s="4">
+      <c r="A10" s="10">
         <v>3007</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2502,18 +2680,18 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1" spans="1:6">
-      <c r="A11" s="4">
+      <c r="A11" s="10">
         <v>3008</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2522,18 +2700,18 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" ht="37" customHeight="1" spans="1:6">
-      <c r="A12" s="4">
+      <c r="A12" s="10">
         <v>3009</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -2541,21 +2719,21 @@
       <c r="E12">
         <v>9</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>110</v>
+      <c r="F12" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="10"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="10"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="10"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2575,48 +2753,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
+      <c r="A1" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="42" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>112</v>
+      <c r="A2" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>65</v>
+        <v>122</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>66</v>
+      <c r="A3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -2624,25 +2802,25 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="10">
         <v>4001</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -2651,18 +2829,18 @@
         <v>1001</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>4002</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -2671,58 +2849,58 @@
         <v>1001</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="10">
         <v>4003</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="10">
         <v>4004</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D7">
         <v>40</v>
       </c>
       <c r="E7">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="10">
         <v>4005</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2731,71 +2909,71 @@
         <v>1002</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="10">
         <v>4006</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
       <c r="E9">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
+      <c r="A10" s="10">
         <v>4007</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D10">
         <v>70</v>
       </c>
       <c r="E10">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4">
+      <c r="A11" s="10">
         <v>4008</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D11">
         <v>80</v>
       </c>
       <c r="E11">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2829,126 +3007,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
+      <c r="A1" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="K1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="M1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="O1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="P1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="Q1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="R1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="S1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:19">
-      <c r="A2" s="2" t="s">
-        <v>146</v>
+      <c r="A2" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>151</v>
+        <v>70</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="H2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="N2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="O2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="1" t="s">
-        <v>66</v>
+      <c r="A3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -3006,14 +3184,14 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="4">
+      <c r="A4" s="10">
         <v>5001</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -3055,24 +3233,24 @@
         <v>3</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="R4" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="S4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="4">
+      <c r="A5" s="10">
         <v>5002</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -3114,24 +3292,24 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="R5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="4">
+      <c r="A6" s="10">
         <v>5003</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -3173,47 +3351,163 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="R6" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="S6" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="10"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="10"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="10"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4"/>
+      <c r="A10" s="10"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="4"/>
-      <c r="G11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="10"/>
+      <c r="G11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="10"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="10"/>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="10"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="10"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="29.75" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>6001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4">
+        <v>500</v>
+      </c>
+      <c r="E4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>6002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5">
+        <v>500</v>
+      </c>
+      <c r="E5" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
